--- a/Trabalho_2/dados/normal/teceiroteste_helicenormal.xlsx
+++ b/Trabalho_2/dados/normal/teceiroteste_helicenormal.xlsx
@@ -5350,11 +5350,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75829867"/>
-        <c:axId val="18432410"/>
+        <c:axId val="71470185"/>
+        <c:axId val="20226223"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75829867"/>
+        <c:axId val="71470185"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5420,7 +5420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18432410"/>
+        <c:crossAx val="20226223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5428,7 +5428,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18432410"/>
+        <c:axId val="20226223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5504,7 +5504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75829867"/>
+        <c:crossAx val="71470185"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10676,11 +10676,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36281970"/>
-        <c:axId val="81356552"/>
+        <c:axId val="4464563"/>
+        <c:axId val="57026934"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36281970"/>
+        <c:axId val="4464563"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10746,7 +10746,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81356552"/>
+        <c:crossAx val="57026934"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10754,7 +10754,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81356552"/>
+        <c:axId val="57026934"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10830,7 +10830,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36281970"/>
+        <c:crossAx val="4464563"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16002,11 +16002,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="28534995"/>
-        <c:axId val="65140535"/>
+        <c:axId val="44088841"/>
+        <c:axId val="47350480"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="28534995"/>
+        <c:axId val="44088841"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16072,7 +16072,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65140535"/>
+        <c:crossAx val="47350480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16080,7 +16080,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65140535"/>
+        <c:axId val="47350480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16156,7 +16156,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28534995"/>
+        <c:crossAx val="44088841"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16876,9 +16876,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>303120</xdr:colOff>
+      <xdr:colOff>302760</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>74520</xdr:rowOff>
+      <xdr:rowOff>74160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -16887,7 +16887,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="190440"/>
-        <a:ext cx="4516920" cy="2741760"/>
+        <a:ext cx="4516560" cy="2741400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -16906,9 +16906,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>303120</xdr:colOff>
+      <xdr:colOff>302760</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>74520</xdr:rowOff>
+      <xdr:rowOff>74160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -16917,7 +16917,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="3238560"/>
-        <a:ext cx="4516920" cy="2741400"/>
+        <a:ext cx="4516560" cy="2741040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -16936,9 +16936,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>303120</xdr:colOff>
+      <xdr:colOff>302760</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>74520</xdr:rowOff>
+      <xdr:rowOff>74160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -16947,7 +16947,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="4213800" y="6286680"/>
-        <a:ext cx="4516920" cy="2741400"/>
+        <a:ext cx="4516560" cy="2741040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
